--- a/downloads/DCT_V1_Ch16_Lab.xlsx
+++ b/downloads/DCT_V1_Ch16_Lab.xlsx
@@ -1599,10 +1599,10 @@
     <t xml:space="preserve">1.4 points against +/-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Fresh paths (seed 26116): the same package's odds (engine)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fitted to the book's paths, it breaches a little more often on new ones</t>
+    <t xml:space="preserve">Fresh paths (certificate seed 26209): the same package's odds (engine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fitted to the book's paths, its odds move by about a standard error on new ones</t>
   </si>
   <si>
     <t xml:space="preserve">Fresh paths: the cheapest package's cost (engine)</t>
@@ -4777,7 +4777,7 @@
         <v>505</v>
       </c>
       <c r="B35" s="27" t="n">
-        <v>0.05247</v>
+        <v>0.04907</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>506</v>
@@ -4788,7 +4788,7 @@
         <v>507</v>
       </c>
       <c r="B36" s="29" t="n">
-        <v>10.8562775776661</v>
+        <v>10.2761119927039</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>508</v>
